--- a/251211/NMDAR_MemoryDysfunction.xlsx
+++ b/251211/NMDAR_MemoryDysfunction.xlsx
@@ -383,11 +383,11 @@
         </is>
       </c>
       <c r="B2">
-        <v>1.0119</v>
+        <v>1.1258</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.9942 – 1.0302</t>
+          <t>0.9436 – 1.3465</t>
         </is>
       </c>
       <c r="D2">
@@ -401,11 +401,11 @@
         </is>
       </c>
       <c r="B3">
-        <v>1.0162</v>
+        <v>1.1742</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.9994 – 1.0336</t>
+          <t>0.9938 – 1.3918</t>
         </is>
       </c>
       <c r="D3">
@@ -419,11 +419,11 @@
         </is>
       </c>
       <c r="B4">
-        <v>1.0106</v>
+        <v>1.1111</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.9949 – 1.0267</t>
+          <t>0.9506 – 1.302</t>
         </is>
       </c>
       <c r="D4">
@@ -437,11 +437,11 @@
         </is>
       </c>
       <c r="B5">
-        <v>1.0076</v>
+        <v>1.0789</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.9927 – 1.0229</t>
+          <t>0.9294 – 1.2542</t>
         </is>
       </c>
       <c r="D5">
@@ -455,11 +455,11 @@
         </is>
       </c>
       <c r="B6">
-        <v>3.8244</v>
+        <v>1.1436</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.8835 – 17.3861</t>
+          <t>0.9877 – 1.3305</t>
         </is>
       </c>
       <c r="D6">
@@ -473,11 +473,11 @@
         </is>
       </c>
       <c r="B7">
-        <v>7.2471</v>
+        <v>1.219</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.8202 – 31.3977</t>
+          <t>1.0617 – 1.4115</t>
         </is>
       </c>
       <c r="D7">
@@ -491,11 +491,11 @@
         </is>
       </c>
       <c r="B8">
-        <v>5.6006</v>
+        <v>1.188</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.5372 – 21.6858</t>
+          <t>1.0439 – 1.3602</t>
         </is>
       </c>
       <c r="D8">
@@ -509,11 +509,11 @@
         </is>
       </c>
       <c r="B9">
-        <v>4.4926</v>
+        <v>1.1621</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.2905 – 16.4538</t>
+          <t>1.0258 – 1.3232</t>
         </is>
       </c>
       <c r="D9">
@@ -527,11 +527,11 @@
         </is>
       </c>
       <c r="B10">
-        <v>1.0172</v>
+        <v>1.1854</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.9973 – 1.0379</t>
+          <t>0.9729 – 1.4501</t>
         </is>
       </c>
       <c r="D10">
@@ -545,11 +545,11 @@
         </is>
       </c>
       <c r="B11">
-        <v>1.021</v>
+        <v>1.2315</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.0022 – 1.0407</t>
+          <t>1.0223 – 1.4903</t>
         </is>
       </c>
       <c r="D11">
@@ -563,11 +563,11 @@
         </is>
       </c>
       <c r="B12">
-        <v>1.0164</v>
+        <v>1.1767</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.9982 – 1.0353</t>
+          <t>0.9823 – 1.4153</t>
         </is>
       </c>
       <c r="D12">
@@ -581,11 +581,11 @@
         </is>
       </c>
       <c r="B13">
-        <v>1.0128</v>
+        <v>1.1362</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.9956 – 1.0307</t>
+          <t>0.9573 – 1.3527</t>
         </is>
       </c>
       <c r="D13">
@@ -599,11 +599,11 @@
         </is>
       </c>
       <c r="B14">
-        <v>1.0064</v>
+        <v>1.0656</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.9919 – 1.0212</t>
+          <t>0.9222 – 1.2335</t>
         </is>
       </c>
       <c r="D14">
@@ -617,11 +617,11 @@
         </is>
       </c>
       <c r="B15">
-        <v>1.0141</v>
+        <v>1.1505</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.9979 – 1.031</t>
+          <t>0.9793 – 1.3565</t>
         </is>
       </c>
       <c r="D15">
@@ -635,11 +635,11 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.995</v>
+        <v>0.951</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.9802 – 1.0098</t>
+          <t>0.8191 – 1.1025</t>
         </is>
       </c>
       <c r="D16">
@@ -653,11 +653,11 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.9932</v>
+        <v>0.9339</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.9785 – 1.0079</t>
+          <t>0.8047 – 1.0814</t>
         </is>
       </c>
       <c r="D17">
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="B18">
-        <v>1.0082</v>
+        <v>1.0856</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.9932 – 1.0237</t>
+          <t>0.9343 – 1.2635</t>
         </is>
       </c>
       <c r="D18">
@@ -689,11 +689,11 @@
         </is>
       </c>
       <c r="B19">
-        <v>1.0114</v>
+        <v>1.12</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.9973 – 1.026</t>
+          <t>0.9731 – 1.2924</t>
         </is>
       </c>
       <c r="D19">
@@ -707,11 +707,11 @@
         </is>
       </c>
       <c r="B20">
-        <v>1.0082</v>
+        <v>1.0856</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.9945 – 1.0224</t>
+          <t>0.9465 – 1.2475</t>
         </is>
       </c>
       <c r="D20">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="B21">
-        <v>1.0071</v>
+        <v>1.0728</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.994 – 1.0204</t>
+          <t>0.9418 – 1.2239</t>
         </is>
       </c>
       <c r="D21">
@@ -743,11 +743,11 @@
         </is>
       </c>
       <c r="B22">
-        <v>1.0144</v>
+        <v>1.1532</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.9923 – 1.0372</t>
+          <t>0.9257 – 1.4413</t>
         </is>
       </c>
       <c r="D22">
@@ -761,11 +761,11 @@
         </is>
       </c>
       <c r="B23">
-        <v>1.0171</v>
+        <v>1.1852</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.9964 – 1.0386</t>
+          <t>0.9649 – 1.4609</t>
         </is>
       </c>
       <c r="D23">
@@ -779,11 +779,11 @@
         </is>
       </c>
       <c r="B24">
-        <v>1.0126</v>
+        <v>1.1333</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.9937 – 1.0322</t>
+          <t>0.9387 – 1.3726</t>
         </is>
       </c>
       <c r="D24">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="B25">
-        <v>1.0109</v>
+        <v>1.1145</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.9928 – 1.0296</t>
+          <t>0.9299 – 1.3388</t>
         </is>
       </c>
       <c r="D25">
@@ -815,11 +815,11 @@
         </is>
       </c>
       <c r="B26">
-        <v>1.0081</v>
+        <v>1.084</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.9931 – 1.0235</t>
+          <t>0.9334 – 1.2611</t>
         </is>
       </c>
       <c r="D26">
@@ -833,11 +833,11 @@
         </is>
       </c>
       <c r="B27">
-        <v>1.0113</v>
+        <v>1.1188</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.9972 – 1.0258</t>
+          <t>0.9724 – 1.2904</t>
         </is>
       </c>
       <c r="D27">
@@ -851,11 +851,11 @@
         </is>
       </c>
       <c r="B28">
-        <v>1.0086</v>
+        <v>1.0892</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.9949 – 1.0227</t>
+          <t>0.9501 – 1.2511</t>
         </is>
       </c>
       <c r="D28">
@@ -869,11 +869,11 @@
         </is>
       </c>
       <c r="B29">
-        <v>1.0078</v>
+        <v>1.0804</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.9947 – 1.0211</t>
+          <t>0.9485 – 1.2326</t>
         </is>
       </c>
       <c r="D29">
